--- a/Compounding_Adjustments_Calculations_Flashcards.xlsx
+++ b/Compounding_Adjustments_Calculations_Flashcards.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -535,66 +535,68 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>สูตรคำนวณปริมาณสารตัวยาที่ต้องชั่งจริงในการเตรียมตำรับ (Theoretical Weighed Amount) ตามหลักเกณฑ์ USP มีสูตรอย่างไร และแต่ละตัวแปรมีความหมายว่าอย่างไร?</t>
+          <t>เภสัชกรต้องการเตรียมยาที่มี Anhydrous theophylline 100.0 mg บนฉลากวัตถุดิบระบุว่ามี Adsorbed moisture (ความชื้นดูดซับ) 0.5% w/w จงคำนวณปริมาณผง Theophylline ที่ต้องชั่งจริง?</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>▶ [สูตรคำนวณหลัก]:
-W = (A × B) / (C × D)
-▶ [ความหมายของตัวแปร]:
-   ↳ W = น้ำหนักของวัตถุดิบตัวยาที่ต้องชั่งจริง (Actual weighed amount)
-   ↳ A = ปริมาณ Active moiety ของตัวยาที่ระบุในสูตรตำรับ (Prescribed active drug weight)
-   ↳ B = มวลโมเลกุล (MW) ของวัตถุดิบที่ใช้ชั่ง (รวมโมเลกุลน้ำผลึก Hydrate และเกลือ Salt)
-   ↳ C = มวลโมเลกุล (MW) ของ Active moiety (โครงสร้างสารออกฤทธิ์แท้จริง เช่น รูป Free base หรือ Free acid)
-   ↳ D = ทศนิยมความบริสุทธิ์ของสาร (Purity decimal factor) คำนวณจาก [% Assay (on dried basis) / 100] × [1 - (LOD % / 100)]
-✦ ข้อยกเว้น / ข้อควรระวัง:
-   ↳ ถ้าสารเป็นรูปบริสุทธิ์ 100% ปราศจากเกลือ น้ำ และความชื้น (Anhydrous pure base) ค่า B=C และ D=1 ดังนั้น W = A</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Compounding Adjustments</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>USP Monograph / IDQ1 Slide P.20</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>เภสัชกรต้องการเตรียมยาที่มี Anhydrous theophylline 100.0 mg บนฉลากวัตถุดิบระบุว่ามี Adsorbed moisture (ความชื้นดูดซับ) 0.5% w/w จงคำนวณปริมาณผง Theophylline ที่ต้องชั่งจริง?</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
           <t>▶ [คำตอบ]:
 ต้องชั่งผง Theophylline จริง = 100.50 mg
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: เข้าใจผลของความชื้น (Adsorbed Moisture)
-     ผงยา 100 mg มีน้ำปนอยู่ 0.5 mg มีเนื้อยาจริงเพียง 99.5 mg
-     ดังนั้น Fraction ของเนื้อยาบริสุทธิ์ = 1 - (0.5 / 100) = 0.995
-   ↳ สเต็ป 2: คำนวณน้ำหนักที่ต้องชั่งจริง (W)
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: เข้าใจผลของความชื้น (Adsorbed Moisture)
+     ผงยา 100 mg มีน้ำปนอยู่ 0.5 mg จึงมีเนื้อยาจริงเพียง 99.5 mg
+     Fraction ของเนื้อยาบริสุทธิ์ = 1 - (0.5 / 100) = 0.995
+   ↳ Step 2: คำนวณน้ำหนักที่ต้องชั่งจริง (W)
      W = ปริมาณตัวยาที่ต้องการ / สัดส่วนเนื้อยาจริง
      W = 100.0 mg / 0.995 = 100.5025 mg ≈ 100.50 mg
 💡 จุดเน้นห้องสอบ:
    ↳ การชดเชยความชื้นหรือ Loss on Drying (LOD) ต้อง 'หาร' ด้วย (1 - Moisture fraction) ทำให้น้ำหนักที่ชั่งจริงต้องมากกว่า 100 mg เสมอ!</t>
         </is>
       </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Compounding Adjustments</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>IDQ1 Slide P.21 Example 1</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ต้องการเตรียม Anhydrous theophylline 250 mg โดยใช้วัตถุดิบ Aminophylline dihydrate ซึ่งมี Adsorbed moisture 0.4% w/w กำหนดให้ 1 mol Aminophylline dihydrate มี Theophylline 2 mol (MW Theophylline = 180.16, MW Aminophylline dihydrate = 456.46) จงคำนวณปริมาณ Aminophylline dihydrate ที่ต้องชั่งจริง?</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+ต้องชั่ง Aminophylline dihydrate จริง = 317.97 mg (≈ 318 mg)
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หา Salt &amp; Hydrate Factor (สัดส่วนโมเลกุล)
+     Aminophylline dihydrate 1 mol (456.46 g) แตกตัวให้ Theophylline 2 mol (2 × 180.16 = 360.32 g)
+     สัดส่วนน้ำหนักสารตั้งต้นต่อเนื้อยา = 456.46 / 360.32 = 1.2668
+   ↳ Step 2: ชดเชยปริมาณเนื้อยาที่ต้องการ 250 mg
+     น้ำหนักในอุดมคติ (ปราศจากความชื้น) = 250 mg × 1.2668 = 316.70 mg
+   ↳ Step 3: ชดเชยความชื้น 0.4% w/w (LOD = 0.004)
+     W = 316.70 mg / (1 - 0.004) = 316.70 / 0.996 = 317.97 mg
+▶ [ใช้สูตรลัด W = (A × B) / (C × D)]:
+   ↳ W = (250 × 456.46) / (360.32 × 0.996) = 317.97 mg</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -603,7 +605,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>IDQ1 Slide P.21 Example 1</t>
+          <t>IDQ1 Slide P.22-23 Example 2</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -618,28 +620,22 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ต้องการเตรียม Anhydrous theophylline 250 mg โดยใช้วัตถุดิบ Aminophylline dihydrate ซึ่งมี Adsorbed moisture 0.4% w/w กำหนดให้ 1 mol Aminophylline dihydrate มี Theophylline 2 mol (MW Theophylline = 180.16, MW Aminophylline dihydrate = 456.46) จงคำนวณปริมาณ Aminophylline dihydrate ที่ต้องชั่งจริง?</t>
+          <t>[ข้อสอบจริง PLE-CC 2561/2563] ถ้าชั่งวัตถุดิบ Acyclovir 150.0 mg วิเคราะห์หาปริมาณตัวยาสำคัญได้ 142.0 mg และวิเคราะห์หาปริมาณน้ำ (Water determination / LOD) ได้ 4.27% วัตถุดิบนี้มี % Assay on anhydrous basis เท่าใด?</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
-ต้องชั่ง Aminophylline dihydrate จริง = 317.97 mg (หรือ ≈ 318 mg)
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: หา Salt &amp; Hydrate Factor (สัดส่วนโมเลกุล)
-     Aminophylline dihydrate 1 mol (456.46 g) แตกตัวให้ Theophylline 2 mol (2 × 180.16 = 360.32 g)
-     สัดส่วนน้ำหนักสารตั้งต้นต่อเนื้อยา = 456.46 / 360.32 = 1.2668
-   ↳ สเต็ป 2: ชดเชยปริมาณเนื้อยาที่ต้องการ 250 mg
-     น้ำหนักในอุดมคติ (ปราศจากความชื้น) = 250 mg × 1.2668 = 316.70 mg
-   ↳ สเต็ป 3: ชดเชยความชื้น 0.4% w/w (LOD = 0.004)
-     W = 316.70 mg / (1 - 0.004) = 316.70 / 0.996 = 317.97 mg
-▶ [ใช้สูตรลัด W = (A × B) / (C × D)]:
-   ↳ A = 250 mg
-   ↳ B = 456.46
-   ↳ C = 2 × 180.16 = 360.32
-   ↳ D = 1 - 0.004 = 0.996
-   ↳ W = (250 × 456.46) / (360.32 × 0.996) = 317.97 mg</t>
+% Assay on anhydrous basis = 98.89% (≈ 98.9%)
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณน้ำหนักวัตถุดิบปราศจากน้ำ (Anhydrous basis weight)
+     น้ำหนักปราศจากน้ำ = 150.0 mg × (1 - 0.0427) = 143.595 mg
+   ↳ Step 2: คำนวณร้อยละของตัวยาสำคัญเทียบกับน้ำหนักแห้ง (% Assay on anhydrous basis)
+     % Assay = (ปริมาณตัวยาสำคัญที่ตรวจพบ / น้ำหนักปราศจากน้ำ) × 100
+     % Assay = (142.0 mg / 143.595 mg) × 100 = 98.889% ≈ 98.9%
+💡 จุดเน้นห้องสอบ:
+   ↳ On anhydrous basis (หรือ On dried basis) หมายถึง ต้องหักน้ำหนักน้ำ/ความชื้นออกก่อน แล้วจึงนำน้ำหนักเนื้อแห้งมาเป็นตัวหาร!</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
@@ -650,7 +646,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>IDQ1 Slide P.22-23 Example 2</t>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2561 &amp; 2563</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -665,7 +661,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>วัตถุดิบ Acetaminophen raw material มีผลวิเคราะห์จาก Certificate of Analysis (CoA) ระบุว่า Loss on Drying (LOD) = 0.3% และมี % Assay on dried basis = 99.2% ถ้าชั่งผงวัตถุดิบนี้มา 50.0 mg จะมีเนื้อตัวยา Acetaminophen บริสุทธิ์ (C8H9NO2) อยู่จริงกี่ mg?</t>
+          <t>วัตถุดิบ Acetaminophen raw material มีผลวิเคราะห์จาก Certificate of Analysis (CoA) ระบุว่า Loss on Drying (LOD) = 0.3% และมี % Assay on dried basis = 99.2% ถ้าชั่งผงวัตถุดิบนี้มา 50.0 mg จะมีเนื้อตัวยา Acetaminophen บริสุทธิ์อยู่จริงกี่ mg?</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
@@ -673,11 +669,11 @@
         <is>
           <t>▶ [คำตอบ]:
 มีเนื้อตัวยา Acetaminophen บริสุทธิ์ = 49.45 mg
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: คำนวณเนื้อสารแห้ง (Dried basis) หลังหักความชื้น
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณเนื้อสารแห้ง (Dried basis) หลังหักความชื้น
      ความชื้น (LOD) = 0.3% → สัดส่วนเนื้อสารแห้ง = 1 - 0.003 = 0.997 (99.7%)
      ผงยา 50.0 mg เป็นเนื้อสารแห้ง = 50.0 × 0.997 = 49.85 mg
-   ↳ สเต็ป 2: คูณความบริสุทธิ์ (% Assay) บน Dried basis
+   ↳ Step 2: คูณความบริสุทธิ์ (% Assay) บน Dried basis
      Assay = 99.2% (0.992)
      เนื้อตัวยาบริสุทธิ์ = 49.85 mg × 0.992 = 49.451 mg ≈ 49.45 mg
 💡 สรุปสูตรจำสั้น:
@@ -717,14 +713,14 @@
           <t>▶ [คำตอบ]:
    ↳ Salt Factor = 1.3869
    ↳ ปริมาณ Amlodipine besylate ที่ต้องชั่ง = 6.93 mg (≈ 6.9 mg)
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: คำนวณ Salt Factor
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณ Salt Factor
      Salt Factor = MW of Salt / MW of Base
      = 567.06 / 408.88 = 1.38686 ≈ 1.3869
-   ↳ สเต็ป 2: หาน้ำหนักเกลือที่ต้องใช้
+   ↳ Step 2: หาน้ำหนักเกลือที่ต้องใช้
      น้ำหนักเกลือ = ปริมาณ Base ที่ต้องการ × Salt Factor
      = 5.0 mg × 1.38686 = 6.934 mg ≈ 6.93 mg
-✦ ข้อยกเว้น / ข้อควรระวัง:
+✦ ข้อควรระวัง:
    ↳ หากโจทย์ถามกลับ: ถ้าในตำรับมี Amlodipine besylate 10 mg จะเทียบเท่า Amlodipine base กี่ mg?
      ตอบ: 10 / 1.3869 = 7.21 mg base</t>
         </is>
@@ -761,11 +757,11 @@
           <t>▶ [คำตอบ]:
    ↳ ใช้ Diclofenac sodium = 53.71 mg
    ↳ ใช้ Diclofenac potassium = 56.43 mg
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ 1. กรณี Diclofenac sodium:
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: กรณี Diclofenac sodium
      Salt Factor = 318.13 / 296.15 = 1.0742
      น้ำหนักเกลือ Na = 50 mg × 1.0742 = 53.71 mg
-   ↳ 2. กรณี Diclofenac potassium:
+   ↳ Step 2: กรณี Diclofenac potassium
      Salt Factor = 334.24 / 296.15 = 1.1286
      น้ำหนักเกลือ K = 50 mg × 1.1286 = 56.43 mg
 💡 ข้อสังเกต:
@@ -795,32 +791,36 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>อะไรคือความแตกต่างระหว่าง % Labeled Amount (%LA) กับ % Assay และมีสูตรคำนวณอย่างไร?</t>
+          <t>ในการตรวจวิเคราะห์ปริมาณตัวยาสำคัญด้วย HPLC โดยวิธี One-point estimation สารละลายมาตรฐาน (Standard solution) ความเข้มข้น Cs = 0.050 mg/mL ให้พื้นที่ใต้พีค (rs) = 250,000 ส่วนสารละลายตัวอย่าง (Sample solution) ปริมาตรรวม 100 mL ให้พื้นที่ใต้พีค (ru) = 265,000 จงคำนวณหาความเข้มข้นตัวอย่าง (Cu) และปริมาณตัวยาสำคัญทั้งหมด (mg)?</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>▶ [ข้อแตกต่างสำคัญ]:
-   ↳ 1. % Labeled Amount (%LA): ใช้กับ 'Finished Product' (ยาสำเร็จรูป เช่น ยาเม็ด ยาน้ำ ยาฉีด) เพื่อตรวจสอบว่ามีปริมาณตัวยาตรงตามที่อ้างบนฉลากหรือไม่
-   ↳ 2. % Assay: ใช้กับ 'Active Pharmaceutical Ingredient (APIs / Raw material)' เพื่อตรวจสอบความบริสุทธิ์ของสารตั้งต้นเทียบกับมาตรฐานทางทฤษฎี
-▶ [สูตรการคำนวณ]:
-   ↳ % Labeled Amount = (Amount of drug found / Labeled amount) × 100
-   ↳ % Assay (Raw material) = (Actual purity content / Theoretical weight) × 100
-✦ เกณฑ์ยอมรับทั่วไป (Acceptance Criteria):
-   ↳ Finished product (%LA): โดยทั่วไปอยู่ในช่วง 90.0% – 110.0% หรือ 95.0% – 105.0% ตามระบุใน Pharmacopoeia monograph
-   ↳ API Raw Material (% Assay): ส่วนใหญ่อยู่ในช่วง 98.0% – 102.0% on dried basis</t>
+          <t>▶ [คำตอบ]:
+   ↳ ความเข้มข้นตัวอย่าง (Cu) = 0.053 mg/mL
+   ↳ ปริมาณตัวยาสำคัญทั้งหมด = 5.30 mg
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณ Cu จากสมการ One-point estimation
+     Cu / Cs = ru / rs  ==&gt;  Cu = Cs × (ru / rs)
+     Cu = 0.050 mg/mL × (265,000 / 250,000)
+     Cu = 0.050 × 1.060 = 0.053 mg/mL
+   ↳ Step 2: คำนวณปริมาณตัวยาทั้งหมดในสารละลาย 100 mL
+     Total amount = Cu × ปริมาตรสารละลายตัวอย่าง
+     = 0.053 mg/mL × 100 mL = 5.30 mg
+✦ เงื่อนไขสำคัญในการใช้ One-Point Estimation:
+   ↳ กราฟมาตรฐานต้องเป็นเส้นตรงผ่านจุดกำเนิด (Pass through zero) และ Cu ต้องใกล้เคียง Cs มาก (±10%)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Compounding Adjustments</t>
+          <t>Instrumental Assay &amp; Titer</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>IDQ1 Slide P.14-16, P.19</t>
+          <t>IDQ1 Slide P.29-30 HPLC Assay</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -835,22 +835,26 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>การหาความเข้มข้นของตัวอย่างด้วยวิธี One-point estimation จากโครมาโทกราฟี (HPLC) มีสูตรคำนวณอย่างไร และมีข้อกำหนดในการใช้งานอย่างไร?</t>
+          <t>การตรวจหาปริมาณ Acetaminophen tablet 500 mg: Standard solution มี Cs = 0.01012 mg/mL ให้ peak area (rs) = 112,500; ส่วน Sample solution มีการเจือจางรวม Dilution Factor = 50,000 เท่า ให้ peak area (ru) = 122,000 จงหาปริมาณ Acetaminophen ในยาเม็ด และ % Labeled Amount?</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>▶ [สูตรคำนวณ One-Point Estimation]:
-Cu / Cs = ru / rs  ==&gt;  Cu = Cs × (ru / rs)
-▶ [ความหมายของตัวแปร]:
-   ↳ Cu = ความเข้มข้นของสารตัวอย่างที่วิเคราะห์ (Sample concentration)
-   ↳ Cs = ความเข้มข้นของสารละลายมาตรฐานอ้างอิง (Standard reference concentration)
-   ↳ ru = สัญญาณตอบสนองของตัวอย่าง เช่น Peak Area หรือ Peak Height (Sample peak response)
-   ↳ rs = สัญญาณตอบสนองของสารละลายมาตรฐาน (Standard peak response)
-✦ เงื่อนไขสำคัญในการใช้ One-Point Estimation:
-   ↳ 1. กราฟมาตรฐานต้องเป็นเส้นตรง (Linearity) และผ่านจุดกำเนิด (Pass through zero)
-   ↳ 2. ความเข้มข้นของสารตัวอย่าง (Cu) ต้องใกล้เคียงกับความเข้มข้นมาตรฐาน (Cs) มาก (อยู่ในช่วง ±10% ของ Cs)</t>
+          <t>▶ [คำตอบ]:
+   ↳ ปริมาณ Acetaminophen ที่ตรวจพบ = 548.7 mg
+   ↳ % Labeled Amount (%LA) = 109.7%
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หาความเข้มข้นของ Sample solution (Cu)
+     Cu = Cs × (ru / rs)
+     Cu = 0.01012 mg/mL × (122,000 / 112,500)
+     Cu = 0.01012 × 1.0844 = 0.010974 mg/mL
+   ↳ Step 2: คำนวณปริมาณยาทั้งหมดที่พบ (Amount found)
+     Amount found = Cu × Dilution Factor
+     = 0.010974 mg/mL × 50,000 mL = 548.7 mg
+   ↳ Step 3: คำนวณ % Labeled Amount
+     %LA = (Amount found / Labeled amount) × 100
+     = (548.7 mg / 500 mg) × 100 = 109.74% ≈ 109.7%</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
@@ -861,7 +865,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>IDQ1 Slide P.29-30 HPLC Assay</t>
+          <t>IDQ1 Slide P.29-31 Comprehensive Example</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -876,26 +880,26 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>การตรวจหาปริมาณ Acetaminophen tablet 500 mg: Standard solution มี Cs = 0.01012 mg/mL ให้ peak area (rs) = 112,500; ส่วน Sample solution มีการเจือจางรวม Dilution Factor = 50,000 เท่า ให้ peak area (ru) = 122,000 จงหาปริมาณ Acetaminophen ในยาเม็ด และ % Labeled Amount?</t>
+          <t>[ข้อสอบแนวสภาฯ / USP Monograph] การวิเคราะห์หา % Assay ของ Aspirin (MW 180.16) ด้วย Residual titration กำหนดให้ Titer ของ 0.5 N NaOH ต่อ Aspirin = 45.04 mg/mL ชั่งผง Aspirin มา 1,500.0 mg ใส่ 0.5 N NaOH 50.0 mL ต้ม 10 นาที ไทเทรต NaOH ส่วนเกินด้วย 0.5 N H2SO4 ใช้ไป 18.20 mL (Blank titration ใช้ 50.00 mL) จงหาปริมาณ Aspirin และ % Assay?</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
-   ↳ ปริมาณ Acetaminophen ที่ตรวจพบ = 548.7 mg
-   ↳ % Labeled Amount (%LA) = 109.7%
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: หาความเข้มข้นของ Sample solution (Cu)
-     Cu = Cs × (ru / rs)
-     Cu = 0.01012 mg/mL × (122,000 / 112,500)
-     Cu = 0.01012 × 1.0844 = 0.010974 mg/mL
-   ↳ สเต็ป 2: คำนวณปริมาณยาทั้งหมดที่พบ (Amount found)
-     Amount found = Cu × Dilution Factor
-     = 0.010974 mg/mL × 50,000 mL = 548.7 mg
-   ↳ สเต็ป 3: คำนวณ % Labeled Amount
-     %LA = (Amount found / Labeled amount) × 100
-     = (548.7 mg / 500 mg) × 100 = 109.74% ≈ 109.7%</t>
+   ↳ ปริมาณ Aspirin ที่ตรวจพบ = 1,432.27 mg
+   ↳ % Assay ของ Aspirin = 95.48%
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หาปริมาตร 0.5 N NaOH ที่ทำปฏิกิริยากับ Aspirin จริง
+     V_reacted = V_blank - V_sample
+     = 50.00 mL - 18.20 mL = 31.80 mL
+   ↳ Step 2: คำนวณปริมาณ Aspirin จากค่า Titer
+     Amount (mg) = V_reacted (mL) × Titer (mg/mL)
+     = 31.80 mL × 45.04 mg/mL = 1,432.27 mg
+   ↳ Step 3: คำนวณ % Assay เทียบกับน้ำหนักที่ชั่งมา
+     % Assay = (1,432.27 mg / 1,500.0 mg) × 100 = 95.48%
+💡 นิยาม Titer:
+   ↳ Titer = น้ำหนัก (mg) ของสารวิเคราะห์ที่ทำปฏิกิริยาสมมูลพอดีกับสารละลายมาตรฐาน 1.00 mL</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
@@ -906,7 +910,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>IDQ1 Slide P.29-31 Comprehensive Example</t>
+          <t>USP Monograph Aspirin Residual Titration</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -921,22 +925,25 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>คำว่า 'Titer' ในการวิเคราะห์ด้วยการไทเทรต (Titrimetric Analysis) หมายถึงอะไร และมีสูตรคำนวณความสัมพันธ์กับน้ำหนักตัวอย่างอย่างไร?</t>
+          <t>การหาปริมาณ Potassium carbonate (K2CO3, MW 138.21) ตามปฏิกิริยา: K2CO3 + 2HCl -&gt; 2KCl + H2O + CO2 จงหาค่า Titer ของ 1 N HCl ต่อ K2CO3 (mg/mL) และถ้าชั่ง K2CO3 มา 1,000 mg ไทเทรตด้วย 1 N HCl ใช้ไป 14.20 mL จงหา % Assay?</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>▶ [นิยามของ Titer]:
-Titer คือ 'ปริมาณหรือน้ำหนักเป็นมิลลิกรัม (mg) ของสารวิเคราะห์ (Analyte)' ที่ทำปฏิกิริยาสมมูลพอดีกับสารละลายมาตรฐาน (Standard titrant) ปริมาตร 1.00 mL
-▶ [สูตรคำนวณ Titer ทางทฤษฎี]:
-Titer (mg/mL) = [MW of analyte / (n × 1000)] × 1000 × Normality of titrant
-= (MW of analyte / n) × Molarity of titrant
-(โดย n คือ Molar ratio ของปฏิกิริยา)
-▶ [สูตรการหา % Purity (% Assay) จาก Titer]:
-% Assay = [V (mL) × Titer (mg/mL) × 100] / Sample weight (mg)
-   ↳ V = ปริมาตรของ Titrant ที่จุดยุติ (Endpoint)
-   ↳ Sample weight = น้ำหนักของตัวอย่างที่ชั่งมาวิเคราะห์</t>
+          <t>▶ [คำตอบ]:
+   ↳ Titer ของ 1 N HCl ต่อ K2CO3 = 69.105 mg/mL
+   ↳ % Assay ของ Potassium carbonate = 98.13%
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณหา Titer
+     K2CO3 1 mol (138.21 g) ทำปฏิกิริยากับ HCl 2 mol (2 equivalents)
+     น้ำหนักสมมูล (Equivalent weight) = 138.21 / 2 = 69.105 g/eq
+     ดังนั้น 1 mL ของ 1 N HCl ทำปฏิกิริยากับ K2CO3 = 69.105 mg
+     ==&gt; Titer = 69.105 mg/mL
+   ↳ Step 2: คำนวณ % Assay
+     % Assay = (V × Titer × 100) / Weight (mg)
+     = (14.20 mL × 69.105 mg/mL × 100) / 1,000 mg
+     = 981.29 / 1,000 × 100 = 98.13%</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
@@ -947,7 +954,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>IDQ1 Slide P.32-34 Titration Analysis</t>
+          <t>IDQ1 Slide P.33-34 K2CO3 Assay</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -962,94 +969,11 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>การหาปริมาณ Potassium carbonate (K2CO3, MW 138.21) ตามปฏิกิริยา: K2CO3 + 2HCl -&gt; 2KCl + H2O + CO2 จงหาค่า Titer ของ 1 N HCl ต่อ K2CO3 (mg/mL) และถ้าชั่ง K2CO3 มา 1,000 mg ไทเทรตด้วย 1 N HCl ใช้ไป 14.20 mL จงหา % Assay?</t>
+          <t>สูตร Master Formula ของ Oral Solution 100 mL ประกอบด้วย: KCl 5 g, Sorbitol sol 30 mL, Saccharin sodium 0.02 g, Methylparaben 0.1 g, Propylparaben 0.01 g, Water qs 100 mL ถ้าต้องการเตรียมจริงเพียง 50 mL จงคำนวณ Working Formula?</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-   ↳ Titer ของ 1 N HCl ต่อ K2CO3 = 69.105 mg/mL
-   ↳ % Assay ของ Potassium carbonate = 98.13%
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: คำนวณหา Titer
-     K2CO3 1 mol (138.21 g) ทำปฏิกิริยากับ HCl 2 mol (2 equivalents)
-     น้ำหนักสมมูล (Equivalent weight) = 138.21 / 2 = 69.105 g/eq
-     ดังนั้น 1 mL ของ 1 N HCl จะทำปฏิกิริยากับ K2CO3 = 69.105 mg
-     ==&gt; Titer = 69.105 mg/mL
-   ↳ สเต็ป 2: คำนวณ % Assay
-     % Assay = (V × Titer × 100) / Weight (mg)
-     % Assay = (14.20 mL × 69.105 mg/mL × 100) / 1,000 mg
-     % Assay = 981.29 / 1,000 × 100 = 98.13%</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Instrumental Assay &amp; Titer</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>IDQ1 Slide P.33-34 K2CO3 Assay</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>หลักการคำนวณ Factor ในการปรับขยายหรือลดสูตรตำรับ (Working Formula Scaling) มีวิธีคิดอย่างไร?</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>▶ [สูตรคำนวณ Scaling Factor]:
-Factor = ปริมาณตำรับที่ต้องการเตรียม (Target Batch Size) / ปริมาณตำรับอ้างอิงตามสูตรหลัก (Master Formula Batch Size)
-▶ [ขั้นตอนการทำ Working Formula]:
-   ↳ สเต็ป 1: คำนวณหาค่า Factor (เป็นตัวเลขไม่มีหน่วย)
-   ↳ สเต็ป 2: นำ Factor ไปคูณกับปริมาณของสารประกอบ 'ทุกตัว' ในสูตรตำรับหลัก
-     Working amount = Master amount × Factor
-   ↳ สเต็ป 3: ตรวจสอบ Minimum Weighable Quantity (MWQ) ของเครื่องชั่ง
-     หากสารตัวใดมีปริมาณน้อยกว่า MWQ (เช่น น้อยกว่า 10 หรือ 20 mg) ห้ามชั่งตรง! ต้องใช้วิธี Aliquot หรือ Stock Solution แทน</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Working Formula &amp; Scaling</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 Lab 1 Introduction</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>สูตร Master Formula ของ Oral Solution 100 mL ประกอบด้วย: KCl 5 g, Sorbitol sol 30 mL, Saccharin sodium 0.02 g, Methylparaben 0.1 g, Propylparaben 0.01 g, Water qs 100 mL ถ้าต้องการเตรียมจริงเพียง 50 mL จงคำนวณ Working Formula?</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ (Working Formula สำหรับ 50 mL)]:
    ↳ Factor = 50 mL / 100 mL = 0.5
@@ -1063,15 +987,105 @@
    ↳ Propylparaben 5 mg น้อยกว่า MWQ ของเครื่องชั่ง 2 ตำแหน่ง จึงต้องเตรียมในรูป Parabens concentrate solution ก่อนนำมาตวงปริมาตร!</t>
         </is>
       </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Working Formula &amp; Scaling</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Lab IDQ4 P.1 Exercise 1</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ต้องการเตรียมสารละลาย Sodium fluoride (NaF) ปริมาตร 100 mL เป็น Stock solution เพื่อนำสารละลายนี้ 0.5 mL ไปเจือจางด้วยน้ำจนครบ 250 mL แล้วได้ความเข้มข้น 2 ppm จงคำนวณปริมาณ NaF ที่ต้องชั่งมาเตรียม Stock solution?</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+ต้องชั่ง NaF = 0.100 g (หรือ 100 mg)
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: เข้าใจหน่วย ppm (Parts Per Million)
+     1 ppm = 1 mg/L = 1 mcg/mL
+     ความเข้มข้น 2 ppm = 2 mg/L = 0.002 mg/mL
+   ↳ Step 2: หาเนื้อตัวยาในสารละลายเจือจาง 250 mL
+     NaF ใน 250 mL = 2 mg/L × 0.250 L = 0.5 mg
+   ↳ Step 3: เนื้อยา 0.5 mg นี้มาจาก Stock solution 0.5 mL
+     ความเข้มข้น Stock solution = 0.5 mg / 0.5 mL = 1.0 mg/mL
+   ↳ Step 4: หาปริมาณ NaF ใน Stock solution 100 mL
+     น้ำหนัก NaF ที่ต้องชั่ง = 1.0 mg/mL × 100 mL = 100 mg = 0.100 g</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Working Formula &amp; Scaling</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Lab IDQ4 P.4 Exercise 5</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>สารละลายเตรียมจาก Calcium chloride dihydrate (CaCl2.2H2O, MW = 147.0) ปริมาณ 1.47 g ละลายในน้ำจนได้ปริมาตร 500 mL จงคำนวณหาปริมาณ Ca2+ ในหน่วย mmol และ mEq พร้อมทั้งหาความเข้มข้นของ Ca2+ และ Cl- ในหน่วย mEq/L?</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+   ↳ ปริมาณ Ca2+ = 10 mmol = 20 mEq
+   ↳ ความเข้มข้น Ca2+ = 40 mEq/L
+   ↳ ความเข้มข้น Cl- = 40 mEq/L
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หาจำนวน mmol ของ CaCl2.2H2O
+     mmol = mg / MW = 1,470 mg / 147.0 = 10 mmol
+     แตกตัวให้ Ca2+ 1 mol (10 mmol) และ Cl- 2 mol (20 mmol)
+   ↳ Step 2: หา mEq (สูตร: mEq = mmol × Valence)
+     - Ca2+ (Valence = 2): 10 mmol × 2 = 20 mEq
+     - Cl- (Valence = 1): 20 mmol × 1 = 20 mEq
+   ↳ Step 3: แปลงเป็นความเข้มข้น mEq/L ในปริมาตร 500 mL
+     - Conc Ca2+ = (20 mEq / 500 mL) × 1,000 mL = 40 mEq/L
+     - Conc Cl- = (20 mEq / 500 mL) × 1,000 mL = 40 mEq/L
+💡 กฎสมดุลประจุไฟฟ้า (Electroneutrality):
+   ↳ ประจุบวก (Cations) และ ประจุลบ (Anions) ในสารละลายต้องมีจำนวน mEq เท่ากันเสมอ (40 mEq/L เท่ากัน)!</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Working Formula &amp; Scaling</t>
+          <t>Milliequivalents (mEq)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Lab IDQ4 P.1 Exercise 1</t>
+          <t>Fundamental Pharmacy Electrolytes</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1086,35 +1100,34 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ต้องการเตรียมสารละลาย Sodium fluoride (NaF) ปริมาตร 100 mL เป็น Stock solution เพื่อนำสารละลายนี้ 0.5 mL ไปเจือจางด้วยน้ำจนครบ 250 mL แล้วได้ความเข้มข้น 2 ppm จงคำนวณปริมาณ NaF ที่ต้องชั่งมาเตรียม Stock solution?</t>
+          <t>[ข้อสอบจริง PLE-CC 2566] แพทย์สั่งจ่ายยา KCl 40 mEq/tablespoon (15 mL) จำนวน 60 mL เภสัชกรต้องเตรียมผง KCl (MW = 74.5) กี่กรัม?</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
-ต้องชั่ง NaF = 0.100 g (หรือ 100 mg)
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: เข้าใจหน่วย ppm (Parts Per Million)
-     1 ppm = 1 mg/L = 1 mcg/mL
-     ความเข้มข้น 2 ppm = 2 mg/L = 0.002 mg/mL
-   ↳ สเต็ป 2: หาเนื้อตัวยาในสารละลายเจือจาง 250 mL
-     NaF ใน 250 mL = 2 mg/L × 0.250 L = 0.5 mg
-   ↳ สเต็ป 3: เนื้อยา 0.5 mg นี้มาจาก Stock solution 0.5 mL
-     ความเข้มข้น Stock solution = 0.5 mg / 0.5 mL = 1.0 mg/mL
-   ↳ สเต็ป 4: หาปริมาณ NaF ใน Stock solution 100 mL
-     น้ำหนัก NaF ที่ต้องชั่ง = 1.0 mg/mL × 100 mL = 100 mg = 0.100 g</t>
+ต้องใช้ผง KCl = 11.92 กรัม
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณหาจำนวน mEq ทั้งหมดใน 60 mL
+     ยา 1 ช้อนโต๊ะ (15 mL) มี KCl = 40 mEq
+     ยา 60 mL คิดเป็น 60 / 15 = 4 ช้อนโต๊ะ
+     ปริมาณ mEq รวม = 4 × 40 mEq = 160 mEq
+   ↳ Step 2: แปลง mEq เป็นกรัม
+     KCl มี Valence = 1 ดังนั้น 160 mEq = 160 mmol
+     น้ำหนัก (mg) = (mEq × MW) / Valence
+     = (160 × 74.5) / 1 = 11,920 mg = 11.92 g</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Working Formula &amp; Scaling</t>
+          <t>Milliequivalents (mEq)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Lab IDQ4 P.4 Exercise 5</t>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2566</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1129,23 +1142,24 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>จงอธิบายสูตรความสัมพันธ์ระหว่าง mEq, mg, mmol และ Valence พร้อมระบุ Valence ของไอออนที่พบบ่อยในข้อสอบสภาฯ?</t>
+          <t>[ข้อสอบจริง PLE-CC 2566] พยาบาลผสม KCl 40 mL (ซึ่งมี KCl 80 mEq) ลงใน NSS 960 mL (ปริมาตรรวม 1,000 mL) แล้วปรับอัตราหยดยาทาง IV เท่ากับ 80 mL/hr ผู้ป่วยรายนี้จะได้รับ KCl กี่ mEq ต่อชั่วโมง?</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>▶ [สูตรคำนวณหลัก]:
-mEq = (mg × Valence) / MW
-mEq = mmol × Valence
-mg = (mEq × MW) / Valence
-▶ [Valence ของไอออนที่ต้องจำขึ้นใจ]:
-   ↳ Monovalent (Valence = 1): Na+, K+, Li+, NH4+, Cl-, HCO3-, F-, Lactate-
-     ==&gt; 1 mEq = 1 mmol เสมอ!
-   ↳ Divalent (Valence = 2): Ca2+, Mg2+, SO4(2-), HPO4(2-)
-     ==&gt; 1 mmol = 2 mEq (หรือ 1 mEq = 0.5 mmol)
-   ↳ Trivalent (Valence = 3): Citrate(3-), PO4(3-), Al3+, Fe3+
-     ==&gt; 1 mmol = 3 mEq</t>
+          <t>▶ [คำตอบ]:
+ผู้ป่วยได้รับ KCl = 6.4 mEq/hr
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หาความเข้มข้นของสารละลายหลังผสม
+     ปริมาตรรวม = 40 mL + 960 mL = 1,000 mL
+     มี KCl รวม = 80 mEq
+     ความเข้มข้น = 80 mEq / 1,000 mL = 0.08 mEq/mL
+   ↳ Step 2: คำนวณอัตราการได้รับยาต่อชั่วโมง
+     IV rate = 80 mL/hr
+     KCl ที่ได้รับ = 80 mL/hr × 0.08 mEq/mL = 6.4 mEq/hr
+✦ ข้อควรระวังทางคลินิก (Safety Limit):
+   ↳ อัตราการให้ KCl ทางหลอดเลือดดำส่วนปลาย (Peripheral line) ทั่วไปไม่ควรเกิน 10 mEq/hr และความเข้มข้นไม่เกิน 40 mEq/L (กรณีนี้ 6.4 mEq/hr จึงปลอดภัย)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
@@ -1156,7 +1170,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Pharmacy Calc</t>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2566</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1180,11 +1194,11 @@
           <t>▶ [คำตอบ]:
    ↳ อัตราเร็วเป็นปริมาตร = 250 mL/hr
    ↳ อัตราหยด (Drip rate) = 63 drops/min (ตอบเป็นจำนวนเต็ม)
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: หาอัตราเร็วเป็น mL/hr
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หาอัตราเร็วเป็น mL/hr
      สารละลาย 40 mEq มีปริมาตร 1,000 mL
      ต้องการให้ยา 10 mEq/hr ==&gt; อัตราเร็ว = (10 mEq × 1,000 mL) / 40 mEq = 250 mL/hr
-   ↳ สเต็ป 2: แปลงเป็น drops/min
+   ↳ Step 2: แปลงเป็น drops/min
      สูตร: Drip rate (drops/min) = [Rate (mL/hr) × Drop factor (drops/mL)] / 60 min
      = (250 × 15) / 60 = 3,750 / 60 = 62.5 drops/min ≈ 63 drops/min
 💡 ข้อมูลเสริมทางคลินิก:
@@ -1214,34 +1228,36 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>[ข้อสอบจริง PLE-CC 2566] แพทย์สั่งจ่ายยา KCl 40 mEq/tablespoon (15 mL) จำนวน 60 mL เภสัชกรต้องเตรียมผง KCl (MW = 74.5) กี่กรัม?</t>
+          <t>[ข้อสอบจริง PLE-CC 2564] ตำรับยาหยอดตาปริมาตร 100 mL ประกอบด้วย: สาร A 0.05 g (E = 0.16), สาร B 0.04 g (E = 0.25), สาร C 0.01 g (E = 0.16) และน้ำกลั่นปรับปริมาตร หากต้องการปรับตำรับนี้ให้เป็นสารละลาย Isotonic จะต้องเติม NaCl กี่กรัม?</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
-ต้องใช้ผง KCl = 11.92 กรัม
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: คำนวณหาจำนวน mEq ทั้งหมดใน 60 mL
-     ยา 1 ช้อนโต๊ะ (15 mL) มี KCl = 40 mEq
-     ยา 60 mL คิดเป็น 60 / 15 = 4 ช้อนโต๊ะ
-     ปริมาณ mEq รวม = 4 × 40 mEq = 160 mEq
-   ↳ สเต็ป 2: แปลง mEq เป็นกรัม
-     KCl มี Valence = 1 ดังนั้น 160 mEq = 160 mmol
-     น้ำหนัก (mg) = (mEq × MW) / Valence
-     = (160 × 74.5) / 1 = 11,920 mg = 11.92 g</t>
+ต้องเติม NaCl = 0.880 กรัม (0.8804 g)
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณความเข้มข้นสมมูลโซเดียมคลอไรด์ของตัวยาทั้งหมด (Σ W × E)
+     - สาร A: 0.05 g × 0.16 = 0.0080 g
+     - สาร B: 0.04 g × 0.25 = 0.0100 g
+     - สาร C: 0.01 g × 0.16 = 0.0016 g
+     ผลรวมสมมูล NaCl = 0.0080 + 0.0100 + 0.0016 = 0.0196 g
+   ↳ Step 2: สารละลาย Isotonic 100 mL ต้องมี NaCl ทั้งหมด 0.900 g (0.9% w/v)
+   ↳ Step 3: คำนวณปริมาณ NaCl ที่ต้องเติมเพิ่ม
+     NaCl ที่ต้องเติม = 0.900 g - 0.0196 g = 0.8804 g ≈ 0.880 g
+💡 จุดเน้นห้องสอบ:
+   ↳ สูตรหา NaCl ที่ต้องเติม = 0.9 - Σ(W × E) ในปริมาตร 100 mL</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Milliequivalents (mEq)</t>
+          <t>Osmolarity &amp; Tonicity</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>ข้อสอบจริงสภาฯ PLE-CC 2566</t>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2564 ข้อ 98</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1256,194 +1272,62 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>[ข้อสอบจริง PLE-CC 2566] พยาบาลผสม KCl 40 mL (ซึ่งมี KCl 80 mEq) ลงใน NSS 960 mL (ปริมาตรรวม 1,000 mL) แล้วปรับอัตราหยดยาทาง IV เท่ากับ 80 mL/hr ผู้ป่วยรายนี้จะได้รับ KCl กี่ mEq ต่อชั่วโมง?</t>
+          <t>ผงเกลือแร่ ORS 1 ซอง ละลายน้ำ 750 mL ประกอบด้วย: Glucose anhydrous 10.125 g (MW 180, i=1), NaCl 1.95 g (MW 58.5, i=2), KCl 1.125 g (MW 74.5, i=2), CaCl2 1.5 g (MW 111, i=3), Sodium citrate dihydrate 2.175 g (MW 294.1, i=4) จงหาค่า Osmolarity รวมของสารละลายนี้ในหน่วย mOsmol/L?</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
-ผู้ป่วยได้รับ KCl = 6.4 mEq/hr
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: หาความเข้มข้นของสารละลายหลังผสม
-     ปริมาตรรวม = 40 mL + 960 mL = 1,000 mL
-     มี KCl รวม = 80 mEq
-     ความเข้มข้น = 80 mEq / 1,000 mL = 0.08 mEq/mL
-   ↳ สเต็ป 2: คำนวณอัตราการได้รับยาต่อชั่วโมง
-     IV rate = 80 mL/hr
-     KCl ที่ได้รับ = 80 mL/hr × 0.08 mEq/mL = 6.4 mEq/hr
-✦ ข้อควรระวังทางคลินิก (Safety Limit):
-   ↳ อัตราการให้ KCl ทางหลอดเลือดดำส่วนปลาย (Peripheral line) โดยทั่วไปไม่ควรเกิน 10 mEq/hr และความเข้มข้นไม่เกิน 40 mEq/L (กรณีนี้ 6.4 mEq/hr จึงปลอดภัย)</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Milliequivalents (mEq)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>ข้อสอบจริงสภาฯ PLE-CC 2566</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>ผงเกลือแร่ ORS 1 ซอง ละลายในน้ำ 750 mL มีส่วนประกอบ: NaCl 1.95 g (MW 58.5), KCl 1.125 g (MW 74.5), CaCl2 1.5 g (MW 111) จงคำนวณความเข้มข้นของ Chloride ion (Cl-) ในสารละลายที่ได้ในหน่วย mEq/L?</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-ความเข้มข้นของ Chloride ion = 100.56 mEq/L (≈ 100.6 mEq/L)
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: หา mEq ของ Cl- จากเกลือแต่ละชนิดใน 1 ซอง
-     1. จาก NaCl (MW 58.5, Valence Cl = 1):
-        mEq = (1,950 mg × 1) / 58.5 = 33.33 mEq
-     2. จาก KCl (MW 74.5, Valence Cl = 1):
-        mEq = (1,125 mg × 1) / 74.5 = 15.10 mEq
-     3. จาก CaCl2 (MW 111, มี Cl สองอะตอม Valence Cl รวม = 2):
-        mEq = (1,500 mg × 2) / 111 = 27.03 mEq
-   ↳ สเต็ป 2: รวม mEq ของ Cl- ทั้งหมดใน 1 ซอง
-     Cl- รวม = 33.33 + 15.10 + 27.03 = 75.46 mEq ในปริมาตร 750 mL
-   ↳ สเต็ป 3: แปลงเป็น mEq ต่อลิตร (mEq/L)
-     mEq/L = (75.46 mEq / 750 mL) × 1,000 mL = 100.61 mEq/L</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Milliequivalents (mEq)</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.5 Exercise 7A</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>สูตรการคำนวณค่า Osmolarity ในหน่วย mOsmol/L มีสูตรอย่างไร และค่า species factor (i) ของสารแต่ละกลุ่มมีค่าเท่าใด?</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>▶ [สูตรการคำนวณ Osmolarity]:
-mOsmol/L = [Weight (g/L) / MW] × i × 1,000
-หรือ
-mOsmol/L = mmol/L × i
-▶ [ค่า Species Factor (i) หรือจำนวนอนุภาคหลังแตกตัว]:
-   ↳ สารที่ไม่แตกตัว (Non-electrolyte): i = 1
-     เช่น Glucose, Dextrose, Sorbitol, Mannitol, Glycerin, Urea
-   ↳ สารที่แตกตัวได้ 2 ไอออน (Binary electrolyte): i = 2
-     เช่น NaCl, KCl, MgSO4
-   ↳ สารที่แตกตัวได้ 3 ไอออน (Ternary electrolyte): i = 3
-     เช่น CaCl2 (1 Ca2+ + 2 Cl-), Na2SO4
-   ↳ สารที่แตกตัวได้ 4 ไอออน: i = 4
-     เช่น Sodium citrate dihydrate (Na3C6H5O7 -&gt; 3 Na+ + 1 Citrate(3-))</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Osmolarity &amp; mOsmol</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>USP &lt;785&gt; Osmolality and Osmolarity</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>ผงเกลือแร่ ORS 1 ซอง ละลายน้ำ 750 mL ประกอบด้วย: Glucose anhydrous 10.125 g (MW 180), NaCl 1.95 g (MW 58.5), KCl 1.125 g (MW 74.5), CaCl2 1.5 g (MW 111), Sodium citrate dihydrate 2.175 g (MW 294.1) จงหาค่า Osmolarity รวมของสารละลายนี้ในหน่วย mOsmol/L?</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
 ค่า Osmolarity รวม = 245.0 mOsmol/L
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: คำนวณ mOsmol ของแต่ละสารใน 1 ซอง
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณ mOsmol ของแต่ละสารใน 1 ซอง (สูตร: [g / MW] × i × 1,000)
      1. Glucose (i=1): (10.125 / 180) × 1 × 1,000 = 56.25 mOsmol
      2. NaCl (i=2): (1.95 / 58.5) × 2 × 1,000 = 66.67 mOsmol
      3. KCl (i=2): (1.125 / 74.5) × 2 × 1,000 = 30.20 mOsmol
      4. CaCl2 (i=3): (1.5 / 111) × 3 × 1,000 = 40.54 mOsmol
      5. Na3Citrate.2H2O (i=4): (2.175 / 294.1) × 4 × 1,000 = 29.58 mOsmol
-   ↳ สเต็ป 2: รวม mOsmol ทั้งหมดในซอง
+   ↳ Step 2: รวม mOsmol ทั้งหมดใน 750 mL
      mOsmol รวม = 56.25 + 66.67 + 30.20 + 40.54 + 29.58 = 183.24 mOsmol ใน 750 mL
-   ↳ สเต็ป 3: เทียบเป็นปริมาตร 1,000 mL (1 L)
+   ↳ Step 3: เทียบเป็นปริมาตร 1,000 mL (1 L)
      Osmolarity = (183.24 mOsmol / 750 mL) × 1,000 mL = 244.32 ≈ 245 mOsmol/L</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Osmolarity &amp; mOsmol</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Osmolarity &amp; Tonicity</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Lab IDQ4 P.5 Exercise 7B</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>จงคำนวณค่า Osmolarity ของน้ำเกลือมาตรฐาน 0.9% w/v Normal Saline (NSS, MW NaCl = 58.44 g/mol) พร้อมแปลผลทางคลินิก?</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>จงคำนวณค่า Osmolarity ของน้ำเกลือมาตรฐาน 0.9% w/v Normal Saline (NSS, MW NaCl = 58.44 g/mol) พร้อมแปลผลเปรียบเทียบกับค่าปกติของพลาสมา?</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
 Osmolarity ของ 0.9% NSS = 308 mOsmol/L (จัดเป็น Isotonic solution)
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: แปลงความเข้มข้นเป็น g/L
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: แปลงความเข้มข้นเป็น g/L
      0.9% w/v = 0.9 g ใน 100 mL ==&gt; 9.0 g ใน 1,000 mL (9 g/L)
-   ↳ สเต็ป 2: คำนวณ mOsmol/L (NaCl แตกตัวให้ Na+ และ Cl- ==&gt; i = 2)
+   ↳ Step 2: คำนวณ mOsmol/L (NaCl แตกตัวให้ Na+ และ Cl- ==&gt; i = 2)
      mOsmol/L = [Weight (g/L) / MW] × i × 1,000
      = (9.0 / 58.44) × 2 × 1,000
      = 0.1540 × 2 × 1,000 = 308.0 mOsmol/L
@@ -1452,228 +1336,373 @@
    ↳ สารน้ำที่มี 280–310 mOsmol/L ถือว่าเป็น Isotonic ต่อเลือดอย่างสมบูรณ์</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Osmolarity &amp; mOsmol</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Osmolarity &amp; Tonicity</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Clinical Fluid &amp; Electrolytes</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>จงคำนวณค่า Osmolarity ของน้ำตาลกลูโคส 5% Dextrose in Water (D5W) ในกรณีที่เตรียมจาก Anhydrous Dextrose (MW 180.16) และ Dextrose monohydrate (MW 198.17)?</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-   ↳ กรณีใช้ Dextrose anhydrous: Osmolarity = 278 mOsmol/L
-   ↳ กรณีใช้ Dextrose monohydrate: Osmolarity = 252 mOsmol/L
-▶ [วิธีคิด]:
-   ↳ 5% w/v = 50 g/L (Dextrose ไม่แตกตัว ==&gt; i = 1)
-   ↳ 1. Anhydrous Dextrose (MW 180.16):
-     mOsmol/L = (50 / 180.16) × 1 × 1,000 = 277.53 ≈ 278 mOsmol/L (Isotonic)
-   ↳ 2. Dextrose monohydrate (MW 198.17):
-     mOsmol/L = (50 / 198.17) × 1 × 1,000 = 252.31 ≈ 252 mOsmol/L (Slightly hypotonic)
-✦ สรุปจุดจำ:
-   ↳ D5W ในขวดมีคุณสมบัติ Isotonic แต่เมื่อฉีดเข้าสู่ร่างกาย กลูโคสจะถูกเซลล์ดึงไปเผาผลาญอย่างรวดเร็ว สารน้ำจะกลายเป็น Free water ซึ่งมีคุณสมบัติทางสรีรวิทยาเป็น Hypotonic!</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Osmolarity &amp; mOsmol</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>USP Monograph Dextrose Injection</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>สูตรการคำนวณค่า Required HLB (rHLB) ของวัฏภาคน้ำมันผสม (Oil phase mixture) ในการเตรียมอิมัลชันมีสูตรอย่างไร?</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>▶ [สูตรการคำนวณ Required HLB ผสม]:
-rHLB(mix) = [ (W1 × rHLB1) + (W2 × rHLB2) + ... + (Wn × rHLBn) ] / W(total oil)
-หรือ
-rHLB(mix) = Σ [ Fraction of oil (i) × rHLB (i) ]
-▶ [ข้อควรระวังสำคัญที่สุดในการสอบ]:
-   ↳ ตัวหาร (Total weight) ต้องใช้น้ำหนักเฉพาะ 'กลุ่มน้ำมัน/ไขมัน' (Oil phase components) เท่านั้น!
-   ↳ ห้ามนำน้ำหนักของน้ำ (Water), Emulsifier หรือส่วนประกอบอื่นมาเป็นตัวหารเด็ดขาด!</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>HLB &amp; Emulsion Blends</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.4 &amp; Physical Pharmacy</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>สูตรตำรับครีมอิมัลชันประกอบด้วย: Mineral oil 35% w/w (rHLB = 12), Wool fat 4% w/w (rHLB = 15), Stearyl alcohol 1% w/w (rHLB = 14), Emulsifiers 10% w/w, Water qs 100% w/w จงหาค่า Required HLB รวมของตำรับนี้?</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
 Required HLB ของตำรับ = 12.35
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: หาผลรวมน้ำหนักของ Oil phase ทั้งหมด
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หาผลรวมน้ำหนักของ Oil phase ทั้งหมด
      Oil phase = Mineral oil (35%) + Wool fat (4%) + Stearyl alcohol (1%) = 40% w/w
-   ↳ สเต็ป 2: คำนวณผลคูณน้ำหนักและ rHLB แต่ละตัว
+   ↳ Step 2: คำนวณผลคูณน้ำหนักและ rHLB แต่ละตัว
      - Mineral oil: 35 × 12 = 420
      - Wool fat: 4 × 15 = 60
      - Stearyl alcohol: 1 × 14 = 14
      ผลรวม (Sum) = 420 + 60 + 14 = 494
-   ↳ สเต็ป 3: หารด้วยน้ำหนักน้ำมันรวม (40%)
-     rHLB = 494 / 40 = 12.35</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr">
+   ↳ Step 3: หารด้วยน้ำหนักน้ำมันรวม (40%)
+     rHLB = 494 / 40 = 12.35
+✦ ข้อควรระวัง:
+   ↳ ตัวหารต้องใช้น้ำหนักเฉพาะ Oil phase (40%) เท่านั้น ห้ามนำน้ำหนักรวมตำรับ (100%) มาหาร!</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>HLB &amp; Emulsion Blends</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Lab IDQ4 P.4 Exercise 6a</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>จากตำรับเดิมที่ต้องการค่า Required HLB = 12.35 โดยใช้สารทำอิมัลชัน 10% w/w ที่เป็นส่วนผสมของ Tween 80 (HLB = 15.0) และ Span 80 (HLB = 4.3) จงคำนวณปริมาณ % w/w ของ Tween 80 และ Span 80 ที่ต้องใช้โดยวิธี Alligation?</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
    ↳ ปริมาณ Tween 80 = 7.52% w/w
    ↳ ปริมาณ Span 80 = 2.48% w/w
 ▶ [วิธีคิดโดย Alligation Alternate]:
-   ↳ สเต็ป 1: วางกากบาทไขว้หาสัดส่วน
+   ↳ Step 1: วางกากบาทไขว้หาสัดส่วน
      Tween 80 (HLB 15.0)       |12.35 - 4.3| = 8.05 ส่วน (Parts of Tween 80)
                      \       /
                       12.35 (Target)
                      /       \
      Span 80 (HLB 4.3)         |15.0 - 12.35| = 2.65 ส่วน (Parts of Span 80)
-   ↳ สเต็ป 2: รวมส่วนทั้งหมด
+   ↳ Step 2: รวมส่วนทั้งหมด
      Total parts = 8.05 + 2.65 = 10.70 ส่วน
-   ↳ สเต็ป 3: เทียบสัดส่วนในปริมาณ Emulsifiers รวม 10% w/w
+   ↳ Step 3: เทียบสัดส่วนในปริมาณ Emulsifiers รวม 10% w/w
      % Tween 80 = (8.05 / 10.70) × 10% = 7.523% ≈ 7.52% w/w
      % Span 80 = (2.65 / 10.70) × 10% = 2.477% ≈ 2.48% w/w
      (ตรวจคำตอบ: 7.52 + 2.48 = 10.00% พอดี)</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>HLB &amp; Emulsion Blends</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Lab IDQ4 P.4 Exercise 6b-c</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>[ข้อสอบจริง PLE-CC 2558] ตำรับยาประกอบด้วย: Mineral oil 30 g (rHLB = 12), Wool fat 1.5 g (rHLB = 10), Cetyl alcohol 1.0 g (rHLB = 15) จงคำนวณหาค่า Required HLB ของตำรับนี้?</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>[ข้อสอบจริง PLE-CC 2558] ตำรับยาประกอบด้วย: Mineral oil 30 g (rHLB = 12), Wool fat 1.5 g (rHLB = 10), Cetyl alcohol 1.0 g (rHLB = 15) จงคำนวณหาค่า Required HLB รวมของตำรับนี้?</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>▶ [คำตอบ]:
 Required HLB ของตำรับ = 12.00
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: รวมน้ำหนักของ Oil phase
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: รวมน้ำหนักของ Oil phase
      Total oil = 30 g + 1.5 g + 1.0 g = 32.5 g
-   ↳ สเต็ป 2: คำนวณผลรวมถ่วงน้ำหนัก
+   ↳ Step 2: คำนวณผลรวมถ่วงน้ำหนัก
      - Mineral oil: 30 × 12 = 360
      - Wool fat: 1.5 × 10 = 15
      - Cetyl alcohol: 1.0 × 15 = 15
      รวม = 360 + 15 + 15 = 390
-   ↳ สเต็ป 3: คำนวณค่า rHLB รวม
+   ↳ Step 3: คำนวณค่า rHLB รวม
      rHLB = 390 / 32.5 = 12.00 พอดี</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>HLB &amp; Emulsion Blends</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2558</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>[ข้อสอบจริง PLE-CC 2567] Aluminum hydroxide (AH) gel ปริมาตร 100 mL มี equivalent of Aluminum oxide อยู่ 4 g หากต้องการเตรียมตำรับ AH gel ปริมาตร 500 mL โดยใช้วัตถุดิบ AHC compress gel ที่มี Aluminum oxide 10% w/w จะต้องใช้ AHC compress gel กี่กรัม?</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+ต้องใช้ AHC compress gel = 200 กรัม
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: หาปริมาณ Aluminum oxide ที่ต้องการใน AH gel 500 mL
+     AH gel 100 mL มี Aluminum oxide = 4 g
+     ดังนั้น AH gel 500 mL ต้องมี Aluminum oxide = (4 g / 100 mL) × 500 mL = 20 g
+   ↳ Step 2: คำนวณหาน้ำหนัก AHC compress gel ที่ต้องชั่ง
+     AHC compress gel มี Aluminum oxide 10% w/w (10 g ใน 100 g)
+     น้ำหนัก AHC compress gel = (20 g × 100 g) / 10 g = 200 g พอดี!
+💡 จุดเน้นห้องสอบ:
+   ↳ โจทย์แนวสภาฯ มักออกเรื่องการคำนวณสารสกัด/Compressed gel ที่คิดเทียบเป็น Equivalent ของออกไซด์หรือเบสบริสุทธิ์</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Compounding Practice Cases</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2567 ข้อ 12</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>[ข้อสอบจริง PLE-CC 2566] ยาเหน็บ Bisacodyl มีค่า Displacement factor (Dv) = 0.2 ต้องการผลิตยาเหน็บขนาด 10 mg จำนวน 10 แท่ง โดยแบบพิมพ์มีน้ำหนักเบสเปล่า 2.0 g ต่อแท่ง จงคำนวณน้ำหนักยาพื้น (Suppository base) รวมที่ต้องเตรียม?</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+ต้องเตรียมน้ำหนักยาพื้นรวม = 19.5 กรัม
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: แปลงหน่วยตัวยาต่อแท่งเป็นกรัม
+     โดสยา = 10 mg = 0.01 g ต่อแท่ง
+   ↳ Step 2: หาปริมาณยาพื้น (Base) ที่ถูกตัวยาแทนที่ต่อแท่ง
+     Base displaced = โดสยา / Dv
+     = 0.01 g / 0.2 = 0.05 g
+   ↳ Step 3: หาน้ำหนักยาพื้นที่ต้องใช้ต่อ 1 แท่ง
+     น้ำหนักยาพื้นต่อแท่ง = น้ำหนักเบสเปล่า - Base displaced
+     = 2.0 g - 0.05 g = 1.95 g/แท่ง
+   ↳ Step 4: คำนวณน้ำหนักยาพื้นสำหรับ 10 แท่ง
+     น้ำหนักยาพื้นรวม = 1.95 g × 10 แท่ง = 19.5 g พอดี!</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Compounding Practice Cases</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2566 Day 2 ข้อ 47</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>[ข้อสอบจริง PLE-CC 2565] ต้องการเตรียมสารละลาย D10W ปริมาตร 500 mL จาก 5% Dextrose in Water (D5W) และ 50% Dextrose in Water (D50W) จะต้องใช้สารละลายแต่ละชนิดอย่างละกี่ mL?</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+   ↳ ใช้ D50W = 55.6 mL (≈ 55 mL)
+   ↳ ใช้ D5W = 444.4 mL (≈ 445 mL)
+▶ [วิธีคิดโดย Alligation Alternate]:
+   ↳ Step 1: ตั้งผัง Alligation Alternate
+     D50W (50%)              |10 - 5|  = 5 ส่วน (Parts of D50W)
+                    \       /
+                       10% (Target)
+                    /       \
+     D5W (5%)                |50 - 10| = 40 ส่วน (Parts of D5W)
+   ↳ Step 2: รวมส่วนทั้งหมด
+     Total parts = 5 + 40 = 45 ส่วน
+   ↳ Step 3: คำนวณปริมาตรใน 500 mL
+     - ปริมาตร D50W = (5 / 45) × 500 mL = 55.56 mL ≈ 55 mL
+     - ปริมาตร D5W = (40 / 45) × 500 mL = 444.44 mL ≈ 445 mL
+     (ตรวจคำตอบ: 55.6 + 444.4 = 500 mL พอดี)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Compounding Practice Cases</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>ข้อสอบจริงสภาฯ PLE-CC 2565 ข้อ 90</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ป่วยเด็กน้ำหนัก 20 kg ได้รับ Favipiravir: วันแรก 60 mg/kg/day แบ่ง bid, วันที่ 2-5 ให้ 20 mg/kg/day แบ่ง bid หากในห้องยามีเฉพาะยาเม็ด 200 mg เภสัชกรเตรียมยาน้ำแขวนตะกอน 70 mL (ความแรง 40 mg/mL) จงหา (1) ขนาดยาเม็ดที่ต้องใช้ทั้งหมด และ (2) ปริมาตรยาน้ำที่เด็กต้องรับประทานต่อครั้งในวันแรกและวันที่ 2-5?</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+   ↳ (1) จำนวนยาเม็ด Favipiravir 200 mg ที่ต้องใช้ = 14 เม็ด
+   ↳ (2) ปริมาตรยาน้ำที่ต้องรับประทาน:
+         - วันแรก: ครั้งละ 15.0 mL (3 ช้อนชา หรือ 1 ช้อนโต๊ะ) bid
+         - วันที่ 2–5: ครั้งละ 5.0 mL (1 ช้อนชา) bid
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณขนาดยาต่อวันและปริมาณยารวม 5 วัน
+     - วันแรก (60 mg/kg): 60 × 20 = 1,200 mg/day (แบ่ง bid = ครั้งละ 600 mg)
+     - วันที่ 2–5 (20 mg/kg): 20 × 20 = 400 mg/day (แบ่ง bid = ครั้งละ 200 mg) รวม 4 วัน = 1,600 mg
+     - ขนาดยารวม 5 วัน = 1,200 + 1,600 = 2,800 mg
+   ↳ Step 2: คำนวณจำนวนยาเม็ด
+     จำนวนเม็ด = 2,800 mg / 200 mg/เม็ด = 14 เม็ด
+   ↳ Step 3: ตรวจสอบปริมาตรยาน้ำต่อครั้ง (ความเข้มข้น 40 mg/mL)
+     - วันแรก: 600 mg / (40 mg/mL) = 15.0 mL
+     - วันที่ 2–5: 200 mg / (40 mg/mL) = 5.0 mL</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Compounding Practice Cases</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Lab IDQ4 P.6 Exercise 9</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>สูตรยา Rx: Indomethacin 25 mg/tsp (5 mL) ปริมาตรรวม 125 mL โดยในห้องยามีเฉพาะ Indomethacin capsule 50 mg/cap ซึ่งแต่ละแคปซูลมีน้ำหนักผงยารวม (ตัวยา + สารเพิ่มปริมาณ) = 100 mg/cap (1) ต้องใช้ตัวยาทั้งหมดกี่แคปซูล (2) หากต้องแกะแคปซูลมาชั่ง ต้องชั่งผงยารวมมากี่ mg?</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>▶ [คำตอบ]:
+   ↳ (1) จำนวนแคปซูลในอุดมคติ = 12.5 แคปซูล (ต้องแกะ 13 แคปซูล)
+   ↳ (2) ปริมาณผงยาที่ต้องชั่งจริง = 1,250 mg
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: คำนวณหาเนื้อยา Indomethacin ทั้งหมดที่ตำรับต้องการ
+     ปริมาตร 125 mL คิดเป็น 125 / 5 = 25 ช้อนชา (tsp)
+     ต้องการตัวยา = 25 × 25 mg = 625 mg Indomethacin
+   ↳ Step 2: คิดเป็นจำนวนแคปซูล (ขนาด 50 mg/cap)
+     จำนวนแคปซูล = 625 mg / 50 mg/cap = 12.5 แคปซูล
+   ↳ Step 3: ชั่งผงยาจากแคปซูล (Aliquot powder)
+     เนื่องจากไม่สามารถแบ่งครึ่งแคปซูลได้ จึงแกะแคปซูลเต็มจำนวนปัดขึ้น = 13 แคปซูล
+     ผงยารวม 13 แคปซูล = 13 × 100 mg = 1,300 mg (มีเนื้อยาจริง 13 × 50 = 650 mg)
+     น้ำหนักผงยาที่ต้องชั่ง = (625 mg / 650 mg) × 1,300 mg = 1,250 mg</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>HLB &amp; Emulsion Blends</t>
+          <t>Compounding Practice Cases</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>ข้อสอบจริงสภาฯ PLE-CC 2558</t>
+          <t>Lab IDQ4 P.5 Exercise 8</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1688,393 +1717,35 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>จงอธิบายความแตกต่างและขั้นตอนการคำนวณระหว่าง Alligation Alternate กับ Alligation Medial?</t>
+          <t>ต้องการเตรียม 50 mL Benzalkonium chloride solution ความเข้มข้น 1:5,000 โดยเตรียมจาก 0.5% w/v Benzalkonium chloride stock solution จงคำนวณปริมาตร stock solution ที่ต้องดูดมาเตรียม?</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>▶ [1. Alligation Alternate (กากบาทไขว้หาสัดส่วน)]:
-   ↳ วัตถุประสงค์: หา 'สัดส่วน' ของสารละลาย 2 ชนิดที่มีความเข้มข้นต่างกัน เพื่อนำมาผสมกันให้ได้ความเข้มข้นเป้าหมายที่ต้องการ
-   ↳ วิธีทำ: นำความเข้มข้นสูงและต่ำวางซ้าย เอาเป้าหมายไว้ตรงกลาง ลบไขว้กันตามแนวทแยง (ใช้ค่าสัมบูรณ์)
-▶ [2. Alligation Medial (การหาความเข้มข้นเฉลี่ย)]:
-   ↳ วัตถุประสงค์: หา 'ความเข้มข้นสุดท้าย' เมื่อนำสารละลายหลายตัวที่ทราบความเข้มข้นและปริมาณแน่นอนแล้วมาเทผสมรวมกัน
-   ↳ สูตร: C(final) = Σ (Amount_i × Conc_i) / Σ (Amount_i)</t>
+          <t>▶ [คำตอบ]:
+ต้องใช้ 0.5% w/v Benzalkonium chloride solution = 2.0 mL
+▶ [วิธีคิดทีละ Step]:
+   ↳ Step 1: แปลง Ratio Strength (1:5,000) เป็น Percentage (% w/v)
+     1:5,000 หมายถึง มีตัวยา 1 g ในสารละลาย 5,000 mL
+     คิดเป็น % w/v = (1 g / 5,000 mL) × 100 = 0.02% w/v
+   ↳ Step 2: ใช้สูตรการเจือจาง C1 × V1 = C2 × V2
+     0.5% × V1 = 0.02% × 50 mL
+     V1 = (0.02 × 50) / 0.5 = 1.0 / 0.5 = 2.0 mL</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Alligation Method</t>
+          <t>Compounding Practice Cases</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Compounding Mathematics</t>
+          <t>Lab IDQ4 P.7 Exercise 10</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>ต้องการเตรียมสารละลาย 70% v/v Ethyl alcohol ปริมาตร 500 mL โดยมี 95% v/v Alcohol และน้ำบริสุทธิ์ (0%) จงคำนวณปริมาตรของ 95% Alcohol และน้ำที่ต้องใช้โดยวิธี Alligation?</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-   ↳ ต้องใช้ 95% Alcohol = 368.4 mL
-   ↳ ต้องใช้น้ำบริสุทธิ์ = 131.6 mL
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: ตั้งผัง Alligation Alternate
-     Alcohol 95%             |70 - 0|  = 70 ส่วน (Parts of 95% Alcohol)
-                    \       /
-                       70%
-                    /       \
-     Water 0%                |95 - 70| = 25 ส่วน (Parts of Water)
-   ↳ สเต็ป 2: รวมส่วนผสม
-     Total parts = 70 + 25 = 95 ส่วน
-   ↳ สเต็ป 3: คำนวณปริมาตรจริงใน 500 mL
-     ปริมาตร 95% Alcohol = (70 / 95) × 500 mL = 368.42 mL ≈ 368.4 mL
-     ปริมาตรน้ำ = (25 / 95) × 500 mL = 131.58 mL ≈ 131.6 mL
-     (หรือเติมน้ำจนครบ 500 mL)</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Alligation Method</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Standard Dilution Problem</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>เภสัชกรนำ Betamethasone dipropionate cream ความเข้มข้น 0.1% w/w จำนวน 20 g มาผสมกับครีมความเข้มข้น 0.05% w/w จำนวน 30 g และ Cream base (0%) อีก 50 g จงหาความเข้มข้นสุดท้ายของครีมผสมนี้โดยวิธี Alligation Medial?</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-ความเข้มข้นสุดท้าย = 0.035% w/w
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: หาน้ำหนักตัวยาในแต่ละส่วนผสม
-     - ส่วนที่ 1: 20 g × 0.1% = 2.0 g (เทียบเท่า 0.02 g drug)
-     - ส่วนที่ 2: 30 g × 0.05% = 1.5 g (เทียบเท่า 0.015 g drug)
-     - ส่วนที่ 3: 50 g × 0% = 0 g drug
-   ↳ สเต็ป 2: รวมผลคูณ (Amount × Conc)
-     Sum = (20 × 0.1) + (30 × 0.05) + (50 × 0)
-     = 2.0 + 1.5 + 0 = 3.5
-   ↳ สเต็ป 3: หารด้วยน้ำหนักครีมรวมทั้งหมด
-     Total weight = 20 + 30 + 50 = 100 g
-     C(final) = 3.5 / 100 g = 0.035% w/w</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Alligation Method</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Alligation Medial Example</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ป่วยเด็กน้ำหนัก 20 kg แพทย์สั่งจ่ายยา Favipiravir 5 วัน: วันแรก 60 mg/kg/day แบ่ง bid หลังจากนั้น 20 mg/kg/day แบ่ง bid อีก 4 วัน ห้องยามียาเม็ด 200 mg แต่เด็กกลืนไม่ได้ เภสัชกรต้องเตรียมยาน้ำแขวนตะกอน (A) วันแรกและวันที่ 2-5 เด็กได้รับยากี่ mg ต่อครั้ง (B) ต้องใช้ยาเม็ด Favipiravir ทั้งหมดกี่เม็ดในการเตรียมตำรับ 5 วันนี้?</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-   ↳ (A) วันแรก: ครั้งละ 600 mg | วันที่ 2-5: ครั้งละ 200 mg
-   ↳ (B) จำนวนยาเม็ด Favipiravir ที่ต้องใช้ทั้งหมด = 14 เม็ด
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ คำถาม A: ขนาดยาต่อครั้ง (แบ่งให้วันละ 2 ครั้ง: bid)
-     - วันแรก (Dose 60 mg/kg/day):
-       ขนาดต่อวัน = 60 mg/kg × 20 kg = 1,200 mg/day
-       แบ่ง bid ==&gt; ครั้งละ 1,200 / 2 = 600 mg ต่อครั้ง
-     - วันที่ 2–5 (Dose 20 mg/kg/day):
-       ขนาดต่อวัน = 20 mg/kg × 20 kg = 400 mg/day
-       แบ่ง bid ==&gt; ครั้งละ 400 / 2 = 200 mg ต่อครั้ง
-   ↳ คำถาม B: จำนวนยาเม็ดทั้งหมดสำหรับ 5 วัน
-     - วันแรก (1 วัน): ได้รับรวม 1,200 mg
-     - วันที่ 2–5 (4 วัน): ได้รับรวม 400 mg/day × 4 วัน = 1,600 mg
-     - ปริมาณยารวม 5 วัน = 1,200 + 1,600 = 2,800 mg
-     - ยาเม็ดความแรง 200 mg/เม็ด ==&gt; จำนวนเม็ด = 2,800 / 200 = 14 เม็ดพอดี!</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Compounding Practice Cases</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.6 Exercise 9</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>จากข้อ Favipiravir สำหรับเด็ก 20 kg หากเภสัชกรเตรียมยาน้ำแขวนตะกอนปริมาตรรวม 70 mL ให้มีความแรง 40 mg/mL (จากยาเม็ด 14 เม็ด) เด็กจะต้องรับประทานยาวันแรก และวันที่ 2-5 ครั้งละกี่ mL?</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-   ↳ วันแรก: รับประทานครั้งละ 15.0 mL
-   ↳ วันที่ 2–5: รับประทานครั้งละ 5.0 mL (1 ช้อนชา)
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: ตรวจสอบความเข้มข้นของยาน้ำ
-     ยา 14 เม็ด = 2,800 mg ในปริมาตรรวม 70 mL
-     ความเข้มข้น = 2,800 mg / 70 mL = 40 mg/mL
-   ↳ สเต็ป 2: คำนวณปริมาตรยาตวงต่อครั้ง
-     - วันแรก (ต้องการ 600 mg/dose):
-       ปริมาตร = 600 mg / (40 mg/mL) = 15.0 mL (เท่ากับ 1 ช้อนโต๊ะ หรือ 3 ช้อนชา)
-     - วันที่ 2–5 (ต้องการ 200 mg/dose):
-       ปริมาตร = 200 mg / (40 mg/mL) = 5.0 mL (เท่ากับ 1 ช้อนชาพอดี)
-   ↳ สเต็ป 3: ตรวจสอบปริมาตรรวมที่ใช้จริงใน 5 วัน
-     (15 mL × 2 ครั้ง) + (5 mL × 2 ครั้ง × 4 วัน) = 30 + 40 = 70 mL พอดี</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Compounding Practice Cases</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.6 Follow-up</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>สูตรยา Rx: Indomethacin 25 mg/tsp (5 mL) ปริมาตรรวม 125 mL โดยในห้องยามีเฉพาะ Indomethacin capsule 50 mg/cap ซึ่งแต่ละแคปซูลมีน้ำหนักผงยารวม (ตัวยา + สารเพิ่มปริมาณ) = 100 mg/cap (a) ต้องใช้ตัวยาทั้งหมดกี่แคปซูล (b) หากต้องแกะแคปซูลมาชั่ง ต้องชั่งผงยารวมมากี่ mg?</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-   ↳ (a) จำนวนแคปซูลในอุดมคติ = 12.5 แคปซูล (ต้องแกะ 13 แคปซูล)
-   ↳ (b) ปริมาณผงยาที่ต้องชั่งจริง = 1,250 mg
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: คำนวณหาเนื้อยา Indomethacin ทั้งหมดที่ตำรับต้องการ
-     ปริมาตร 125 mL คิดเป็น 125 / 5 = 25 ช้อนชา (tsp)
-     ต้องการตัวยา = 25 × 25 mg = 625 mg Indomethacin
-   ↳ สเต็ป 2: คิดเป็นจำนวนแคปซูล (ขนาด 50 mg/cap)
-     จำนวนแคปซูล = 625 mg / 50 mg/cap = 12.5 แคปซูล
-   ↳ สเต็ป 3: ชั่งผงยาจากแคปซูล (Aliquot powder)
-     เนื่องจากไม่สามารถแบ่งครึ่งแคปซูลได้ จึงต้องแกะแคปซูลเต็มจำนวนปัดขึ้น = 13 แคปซูล
-     ผงยารวม 13 แคปซูล = 13 × 100 mg = 1,300 mg (ซึ่งมีเนื้อยาจริง 13 × 50 = 650 mg)
-     บัญญัติไตรยางศ์หาผงยาที่ให้เนื้อยา 625 mg:
-     น้ำหนักผงยาที่ต้องชั่ง = (625 mg / 650 mg) × 1,300 mg = 1,250 mg</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Compounding Practice Cases</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.5 Exercise 8</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>ต้องการเตรียม 50 mL Benzalkonium chloride solution ความเข้มข้น 1:5,000 โดยเตรียมจาก 0.5% w/v Benzalkonium chloride stock solution จงคำนวณปริมาตร stock solution ที่ต้องดูดมาเตรียม?</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-ต้องใช้ 0.5% w/v Benzalkonium chloride solution = 2.0 mL
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: แปลง Ratio Strength (1:5,000) เป็น Percentage (% w/v)
-     1:5,000 หมายถึง มีตัวยา 1 g ในสารละลาย 5,000 mL
-     คิดเป็น % w/v = (1 g / 5,000 mL) × 100 = 0.02% w/v
-   ↳ สเต็ป 2: ใช้สูตรการเจือจาง C1 × V1 = C2 × V2
-     C1 = 0.5% w/v
-     V1 = ปริมาตร stock ที่ต้องการหา
-     C2 = 0.02% w/v
-     V2 = 50 mL
-     0.5% × V1 = 0.02% × 50 mL
-     V1 = (0.02 × 50) / 0.5 = 1.0 / 0.5 = 2.0 mL</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Compounding Practice Cases</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.7 Exercise 10</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>ต้องการเตรียม Antiseptic solution ปริมาตร 100 mL ให้มี Chlorhexidine gluconate ความแรง 2% w/v โดยในห้องยามีสารละลายเข้มข้น 20% w/v Chlorhexidine gluconate solution จงคำนวณปริมาตรของสารละลาย 20% ที่ต้องใช้?</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-ต้องใช้ 20% w/v Chlorhexidine gluconate solution = 10.0 mL
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: ใช้สมการเจือจาง C1 × V1 = C2 × V2
-     C1 = 20% w/v
-     V1 = ปริมาตรที่ต้องตวง
-     C2 = 2% w/v
-     V2 = 100 mL
-   ↳ สเต็ป 2: คำนวณหา V1
-     20% × V1 = 2% × 100 mL
-     V1 = 200 / 20 = 10.0 mL
-💡 คำแนะนำการผสมจริง:
-   ↳ ตวง 20% Chlorhexidine gluconate 10.0 mL ใส่ขวดรูปชมพู่ ผสมกับ Isopropyl alcohol 70 mL และสี Brilliant blue แล้วปรับปริมาตรด้วย Purified water จนครบ 100 mL</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Compounding Practice Cases</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.7 Exercise 11</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>สูตรตำรับยาขี้ผึ้ง: Benzoin Tincture 18 mL (Specific gravity = 0.88), Peru Balsam 10 g, Cream base ad to 70 g จงหา (1) ความเข้มข้นของ Benzoin Tincture ในตำรับนี้เป็น % w/w และ (2) ปริมาณ Cream base ที่ต้องชั่งมาเตรียม?</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>▶ [คำตอบ]:
-   ↳ (1) ความแรงของ Benzoin Tincture = 22.63% w/w
-   ↳ (2) ปริมาณ Cream base ที่ต้องชั่ง = 44.16 g
-▶ [วิธีคิดทีละสเต็ป]:
-   ↳ สเต็ป 1: แปลงปริมาตร (mL) ของ Benzoin Tincture เป็นน้ำหนัก (g) โดยใช้ Specific Gravity
-     น้ำหนัก (g) = ปริมาตร (mL) × Specific gravity
-     = 18 mL × 0.88 g/mL = 15.84 g
-   ↳ สเต็ป 2: คำนวณความเข้มข้นในตำรับ (% w/w)
-     น้ำหนักตำรับทั้งหมด = 70 g
-     % w/w Benzoin Tincture = (15.84 g / 70 g) × 100 = 22.628% ≈ 22.63% w/w
-   ↳ สเต็ป 3: คำนวณปริมาณ Cream base ที่ต้องชั่ง
-     Cream base = น้ำหนักรวม - น้ำหนักสารอื่นๆ
-     = 70 g - (15.84 g + 10 g)
-     = 70 g - 25.84 g = 44.16 g</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Compounding Practice Cases</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Lab IDQ4 P.4 Exercise 4</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
